--- a/docs/test/unit/NOUS-104/観点表_retryPolicy.xlsx
+++ b/docs/test/unit/NOUS-104/観点表_retryPolicy.xlsx
@@ -13,9 +13,9 @@
     <sheet name="対象概要" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'観点表'!$A$4:$Q$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'観点表'!$A$4:$Q$41</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'観点表'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'テストデータ'!$A$4:$F$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'テストデータ'!$A$4:$F$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -871,7 +871,7 @@
       <c r="Q7" s="7" t="inlineStr">
         <is>
           <t>既存テスト：実装時のテスト（NOUS-63）
-確認事項 3</t>
+実施の手がかり</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       <c r="Q8" s="7" t="inlineStr">
         <is>
           <t>既存テスト：実装時のテスト（NOUS-63）
-確認事項 3</t>
+実施の手がかり</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,8 @@
       <c r="Q10" s="7" t="inlineStr">
         <is>
           <t>既存テスト：実装時のテスト（NOUS-63）
-確認事項 1・3</t>
+疑い：後半は runs の上限で StoppedError を期待しており、疑い 2（再試行は runs の上限では止めない）と食い違う
+疑い 2、実施の手がかり</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1505,7 @@
       <c r="Q16" s="7" t="inlineStr">
         <is>
           <t>既存テスト：実装時のテスト（NOUS-83）
-確認事項 3</t>
+実施の手がかり</t>
         </is>
       </c>
     </row>
@@ -2516,13 +2517,13 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>world_settings が無いときは ctx.settings の上限で判定し、上限なら StoppedError</t>
+          <t>world_settings が無いときは ctx.settings の Neurons の上限で判定し、上限なら StoppedError</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>前提：一時 DB（createTestDb）、FakeClock 2026-10-22T09:00:00.000Z、world_settings の無い世界、daily_usage runs=5
-入力：timeout、settings={neurons 9500, runs 5}</t>
+          <t>前提：一時 DB（createTestDb）、FakeClock 2026-10-22T09:00:00.000Z、world_settings の無い世界、daily_usage neurons=100
+入力：timeout、settings={neurons 100, runs 480}</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -2544,7 +2545,7 @@
       <c r="L31" s="5" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>TC-UT_RTY-014 world_settings が無いときは ctx.settings の上限で判定し、上限に達していれば StoppedError を投げる</t>
+          <t>TC-UT_RTY-014 world_settings が無いときは ctx.settings の Neurons の上限で判定し、上限に達していれば StoppedError を投げる</t>
         </is>
       </c>
       <c r="N31" s="6" t="inlineStr">
@@ -2556,7 +2557,8 @@
       <c r="P31" s="6" t="inlineStr"/>
       <c r="Q31" s="7" t="inlineStr">
         <is>
-          <t>既存テスト：なし</t>
+          <t>既存テスト：なし
+疑い 2 の決定により、上限の判定は Neurons で見る</t>
         </is>
       </c>
     </row>
@@ -2868,18 +2870,18 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>呼び出しが成功した直後に signal が abort されていたら CancelledError、試行は記録しない</t>
+          <t>呼び出しが成功した直後に signal が abort されていても、その試行をトークン・Neurons 付きで記録してから CancelledError</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
           <t>前提：一時 DB（createTestDb）、FakeClock 2026-10-22T09:00:00.000Z
-入力：abort してから成功を返す呼び出し</t>
+入力：abort してから成功（トークン 500・25、Neurons 5.2）を返す呼び出し</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>ClockCancelledError、試行 0 件</t>
+          <t>ClockCancelledError、試行 1 件（cancelled、prompt_tokens 500、Neurons 5.2）、daily_usage calls=1・runs=1・Neurons 5.2</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -2896,7 +2898,7 @@
       <c r="L36" s="5" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr">
         <is>
-          <t>TC-UT_RTY-019 呼び出しが成功した直後に signal が abort されていたら CancelledError を投げ、試行は記録しない</t>
+          <t>TC-UT_RTY-019 呼び出しが成功した直後に signal が abort されていても、その試行を Neurons 付きで記録してから CancelledError を投げる</t>
         </is>
       </c>
       <c r="N36" s="6" t="inlineStr">
@@ -2909,7 +2911,8 @@
       <c r="Q36" s="7" t="inlineStr">
         <is>
           <t>既存テスト：なし
-確認事項 2。設計書に記載なし。実装の値</t>
+疑い：実装は試行を記録せずに CancelledError を投げる（疑い 4）
+2026-10-26 Kouhei Tajima の決定：緊急停止の直後も試行を記録する。result は確認事項 1</t>
         </is>
       </c>
     </row>
@@ -3194,9 +3197,81 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>TC-UT_RTY-024</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>callWithRetry</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>正常系</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>境界値</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>この生成イベントの 1 回目で runs が日次上限（1）に達しても、待ちの後に再試行する（runs の上限では止めない）</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>前提：一時 DB（createTestDb）、FakeClock 2026-10-22T09:00:00.000Z、runs 上限 1・Neurons 上限 9500 の世界
+入力：timeout の後に成功</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>attemptNo=2、呼び出し 2 回</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>B21-T, B22-F</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>FakeClock 2026-10-22T09:00:00.000Z、呼び出しの関数</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr"/>
+      <c r="L41" s="5" t="inlineStr"/>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>TC-UT_RTY-024 この生成イベントの 1 回目で runs が日次上限に達しても、待ちの後に再試行する（runs の上限では止めない）</t>
+        </is>
+      </c>
+      <c r="N41" s="6" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="O41" s="6" t="inlineStr"/>
+      <c r="P41" s="6" t="inlineStr"/>
+      <c r="Q41" s="7" t="inlineStr">
+        <is>
+          <t>既存テスト：一部 TC-NOUS63_DEV-12（runs の上限で止まることを期待しており逆）
+疑い：実装は runs の上限でも StoppedError にする（疑い 2）
+2026-10-26 Kouhei Tajima の決定：再試行は Neurons の上限だけで止める</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:Q40"/>
-  <conditionalFormatting sqref="A5:Q90">
+  <autoFilter ref="A4:Q41"/>
+  <conditionalFormatting sqref="A5:Q91">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$N5="NG"</formula>
     </cfRule>
@@ -3208,10 +3283,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N5:N90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N5:N91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未実施,OK,NG,保留,対象外"</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5:D91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"正常系,異常系"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3263,7 +3338,7 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>COUNTA(観点表!$B$5:$B$90)</f>
+        <f>COUNTA(観点表!$B$5:$B$91)</f>
         <v/>
       </c>
     </row>
@@ -3274,7 +3349,7 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>COUNTIF(観点表!$D$5:$D$90,"正常系")</f>
+        <f>COUNTIF(観点表!$D$5:$D$91,"正常系")</f>
         <v/>
       </c>
     </row>
@@ -3285,7 +3360,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>COUNTIF(観点表!$D$5:$D$90,"異常系")</f>
+        <f>COUNTIF(観点表!$D$5:$D$91,"異常系")</f>
         <v/>
       </c>
     </row>
@@ -3305,7 +3380,7 @@
         </is>
       </c>
       <c r="B10" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$90,"エラー処理")</f>
+        <f>COUNTIF(観点表!$E$5:$E$91,"エラー処理")</f>
         <v/>
       </c>
     </row>
@@ -3316,7 +3391,7 @@
         </is>
       </c>
       <c r="B11" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$90,"依存")</f>
+        <f>COUNTIF(観点表!$E$5:$E$91,"依存")</f>
         <v/>
       </c>
     </row>
@@ -3327,7 +3402,7 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$90,"分岐網羅")</f>
+        <f>COUNTIF(観点表!$E$5:$E$91,"分岐網羅")</f>
         <v/>
       </c>
     </row>
@@ -3338,7 +3413,7 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$90,"同値分割")</f>
+        <f>COUNTIF(観点表!$E$5:$E$91,"同値分割")</f>
         <v/>
       </c>
     </row>
@@ -3349,7 +3424,7 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$90,"境界値")</f>
+        <f>COUNTIF(観点表!$E$5:$E$91,"境界値")</f>
         <v/>
       </c>
     </row>
@@ -3360,7 +3435,7 @@
         </is>
       </c>
       <c r="B15" s="10">
-        <f>COUNTIF(観点表!$E$5:$E$90,"開発者テスト")</f>
+        <f>COUNTIF(観点表!$E$5:$E$91,"開発者テスト")</f>
         <v/>
       </c>
     </row>
@@ -3380,7 +3455,7 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIF(観点表!$K$5:$K$90,"?*")</f>
+        <f>COUNTIF(観点表!$K$5:$K$91,"?*")</f>
         <v/>
       </c>
     </row>
@@ -3411,7 +3486,7 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$90,"未実施")</f>
+        <f>COUNTIF(観点表!$N$5:$N$91,"未実施")</f>
         <v/>
       </c>
     </row>
@@ -3422,7 +3497,7 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$90,"OK")</f>
+        <f>COUNTIF(観点表!$N$5:$N$91,"OK")</f>
         <v/>
       </c>
     </row>
@@ -3433,7 +3508,7 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$90,"NG")</f>
+        <f>COUNTIF(観点表!$N$5:$N$91,"NG")</f>
         <v/>
       </c>
     </row>
@@ -3444,7 +3519,7 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$90,"保留")</f>
+        <f>COUNTIF(観点表!$N$5:$N$91,"保留")</f>
         <v/>
       </c>
     </row>
@@ -3455,7 +3530,7 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIF(観点表!$N$5:$N$90,"対象外")</f>
+        <f>COUNTIF(観点表!$N$5:$N$91,"対象外")</f>
         <v/>
       </c>
     </row>
@@ -3492,7 +3567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4077,7 +4152,7 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>world_settings が無いときは ctx.settings の上限で判定し、上限なら StoppedError</t>
+          <t>world_settings が無いときは ctx.settings の Neurons の上限で判定し、上限なら StoppedError</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
@@ -4177,7 +4252,7 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>呼び出しが成功した直後に signal が abort されていたら CancelledError、試行は記録しない</t>
+          <t>呼び出しが成功した直後に signal が abort されていても、その試行をトークン・Neurons 付きで記録してから CancelledError</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -4269,8 +4344,28 @@
       <c r="E40" s="13" t="inlineStr"/>
       <c r="F40" s="13" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>TC-UT_RTY-024</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>この生成イベントの 1 回目で runs が日次上限（1）に達しても、待ちの後に再試行する（runs の上限では止めない）</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>未作成</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="inlineStr"/>
+      <c r="E41" s="13" t="inlineStr"/>
+      <c r="F41" s="13" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F40"/>
+  <autoFilter ref="A4:F41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -4282,7 +4377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4770,37 +4865,45 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>・確認事項 1：runs の上限ちょうど。この生成イベントの最初の試行で daily_usage.runs が上限に達すると、待ちの後の上限の確認で StoppedError になり、上限の中で始めた最後の 1 回が再試行できない（TC-NOUS63_DEV-12 がこの動きを期待している）。runs は「LLM を呼んだ生成イベントの数」なので、同じイベントの再試行は runs の上限で止めない方が設計の意図に近いと考える。仕様の確認を求める</t>
+          <t>・疑い 2：再試行は runs の上限では止めず、Neurons の上限だけで止めるのが仕様（2026-10-26 Kouhei Tajima の決定）。実装は待ちの後の上限の確認に isWithinLimits（Neurons と runs の両方）を使うため、この生成イベントの最初の試行で daily_usage.runs が上限に達すると StoppedError になり、上限の中で始めた最後の 1 回が再試行できない。TC-UT_RTY-024 は仕様の期待結果で書いた（実施で NG の見込み）。TC-NOUS63_DEV-12 の後半は runs の上限で StoppedError を期待しており、仕様と食い違う</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>・確認事項 2：呼び出しが成功した直後に signal が abort されると、試行を記録せずに CancelledError になる（TC-UT_RTY-019）。消費した Neurons が daily_usage に入らない。緊急停止のときだけで影響は小さい。設計書に記載がないため、テストは実装の値で書いた</t>
+          <t>・疑い 4：呼び出しが成功した直後に緊急停止（signal の abort）されても、その試行は記録するのが仕様（2026-10-26 Kouhei Tajima の決定）。実装は試行を記録せずに CancelledError を投げるため、消費した Neurons が daily_usage に入らない。TC-UT_RTY-019 は仕様の期待結果（result=cancelled、トークン・Neurons 付きで記録）で書いた。result を cancelled とするか ok とするかは設計書に記載がなく、検証の前に取り消されるため cancelled とした（確認事項 1）</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>・確認事項 3：TC-NOUS63_DEV-09・10・12、TC-NOUS83_DEV-04 は、callWithRetry を呼んだ直後に clock.advance するため、sleep が張られる前に時刻が進む可能性がある（FakeClock.advance は呼んだ時点のタイマーだけを解決する）。実施のときに落ちたら、テストの書き方の問題として切り分ける。UT ではタイマーが張られるのを待ってから進めている</t>
+          <t>・実施の手がかり：TC-NOUS63_DEV-09・10・12、TC-NOUS83_DEV-04 は、callWithRetry を呼んだ直後に clock.advance するため、sleep が張られる前に時刻が進む可能性がある（FakeClock.advance は呼んだ時点のタイマーだけを解決する）。実施のときに落ちたら、まずテストの書き方の問題として切り分ける。UT ではタイマーが張られるのを待ってから進めている</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="18" t="inlineStr">
         <is>
+          <t>・確認事項 1：緊急停止の直後の試行の result（cancelled か ok か）。TC-UT_RTY-019 は cancelled で書いた</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
           <t>・分岐 B12 の真（startAttemptNo が 5 以上）は TC-NOUS63_DEV-13 で通る。opportunityRunner からは 5 以上で呼ばれることはない</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A39:C39"/>
     <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A37:C37"/>
     <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
